--- a/KURIKULUM2026_REVISI/042_LAPORAN_AUDIT_KESELARASAN_KURIKULUM_DAN_BOUNDARY_OF_TOPICS.xlsx
+++ b/KURIKULUM2026_REVISI/042_LAPORAN_AUDIT_KESELARASAN_KURIKULUM_DAN_BOUNDARY_OF_TOPICS.xlsx
@@ -556,12 +556,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Typo penomoran `STI-628` pada baris Smart City (seharusnya `STI-625`) dan penulisan PBO sebagai `STI-206`.</t>
+          <t>Typo penomoran `STI-628` pada baris Smart City (seharusnya `STI-727`) dan penulisan PBO sebagai `STI-206`.</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Diperbaiki menjadi `STI-625 Smart City &amp; Pemerintahan Digital (2 SKS)` dan pemodelan pasangan ke-3 diselaraskan ke `FST-102 &amp; FST-203 vs STI-309 RPL`.</t>
+          <t>Diperbaiki menjadi `STI-727 Smart City &amp; Pemerintahan Digital (2 SKS)` dan pemodelan pasangan ke-3 diselaraskan ke `FST-102 &amp; FST-203 vs STI-309 RPL`.</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Menyelaraskan alur Sem 6-7 dengan memasukkan `STI-625`, `FST-611`, `STI-728`; memperbarui rujukan kode peminatan ke `STA-501`, `STB-501`, `STC-501`.</t>
+          <t>Menyelaraskan alur Sem 6-7 dengan memasukkan `STI-727`, `FST-611`, `STI-728`; memperbarui rujukan kode peminatan ke `STA-501`, `STB-501`, `STC-501`.</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
